--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/oct-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -900,7 +900,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2859-1212-CM26</t>
+          <t>2322-777-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -940,28 +940,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12661.84</v>
+        <v>6765.22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1036569-158-CM26</t>
+          <t>2859-1212-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -986,17 +990,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1016,13 +1020,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>42677.44</v>
+        <v>12661.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4794-103-CM26</t>
+          <t>1036569-158-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1037,7 +1041,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1047,27 +1051,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1077,13 +1081,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>25721.1</v>
+        <v>42677.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057922-69-CM26</t>
+          <t>4794-103-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1098,7 +1102,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1108,27 +1112,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1138,13 +1142,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>149242.35</v>
+        <v>25721.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2322-801-CM26</t>
+          <t>1417966-83-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1159,7 +1163,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1169,27 +1173,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>65.063.166-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>CORPORACIÓN DESARROLLA BIOBÍO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1203,13 +1207,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>26770.61</v>
+        <v>9972.780000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1175-939-CM26</t>
+          <t>1057922-69-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1234,47 +1238,43 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>21831.11</v>
+        <v>149242.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4679-80-CM26</t>
+          <t>2322-801-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1299,27 +1299,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6823.9</v>
+        <v>26770.61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5066-247-CM26</t>
+          <t>1175-939-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12184.8</v>
+        <v>21831.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>629373-275-CM26</t>
+          <t>4679-80-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1429,27 +1429,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.962.500-4</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45132.22</v>
+        <v>6823.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1079650-169-CM26</t>
+          <t>5066-247-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1494,43 +1494,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11308.33</v>
+        <v>12184.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057448-477-CM26</t>
+          <t>629373-275-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,7 +1549,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1555,27 +1559,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>70.962.500-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1589,13 +1593,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5392.87</v>
+        <v>45132.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057448-478-CM26</t>
+          <t>1233616-1907-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1620,43 +1624,47 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Plusmedical SpA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.520.087-3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8351.77</v>
+        <v>12551.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057448-479-CM26</t>
+          <t>1057448-481-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1696,32 +1704,28 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10483.81</v>
+        <v>7208.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057448-481-CM26</t>
+          <t>1057448-479-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1761,28 +1765,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7208.87</v>
+        <v>10483.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1233616-1907-CM26</t>
+          <t>1057448-477-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1807,27 +1815,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1841,13 +1849,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12551.44</v>
+        <v>5392.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4794-104-CM26</t>
+          <t>1079650-169-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1862,7 +1870,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1872,27 +1880,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1902,13 +1910,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>60771.52</v>
+        <v>11308.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1475044-78-CM26</t>
+          <t>1057448-478-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1923,7 +1931,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1933,27 +1941,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>Plusmedical SpA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>76.520.087-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1963,13 +1971,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>60463.1</v>
+        <v>8351.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057448-488-CM26</t>
+          <t>1057882-13-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1984,7 +1992,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1994,17 +2002,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2024,13 +2032,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9795.200000000001</v>
+        <v>15221.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5640-56-CM26</t>
+          <t>4794-104-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2085,13 +2093,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>58999.19</v>
+        <v>60771.52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5640-57-CM26</t>
+          <t>1475044-78-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2146,13 +2154,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>58487.38</v>
+        <v>60463.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1436733-158-CM26</t>
+          <t>1057448-488-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2167,7 +2175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2177,27 +2185,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.981.060-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2207,13 +2215,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6764.94</v>
+        <v>9795.200000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>593951-250-CM26</t>
+          <t>5640-56-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2228,7 +2236,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2238,12 +2246,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2253,32 +2261,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>141171.63</v>
+        <v>58999.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5529-105-CM26</t>
+          <t>5640-57-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2293,7 +2297,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2318,91 +2322,534 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7994.81</v>
+        <v>58487.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>1436733-158-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.981.060-0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>6764.94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>593951-250-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>141171.63</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>758-812-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>60.509.001-k</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>17156.05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>5529-105-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>7994.81</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3495-303-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>12646.02</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1208110-42-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>33575.46</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>5482-207-CM26</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>69.070.500-1</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>12783.28</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5952-207-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>26921.38</v>
       </c>
     </row>
   </sheetData>
